--- a/220V供电300W四路彩屏桌面电源（已完结）/制作图纸和BOM/BOM_300W 四路彩屏桌面电源_2025-06-03.xlsx
+++ b/220V供电300W四路彩屏桌面电源（已完结）/制作图纸和BOM/BOM_300W 四路彩屏桌面电源_2025-06-03.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Desktop\复刻计划\300W电源\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Documents\GitHub\open-source-projects\220V供电300W四路彩屏桌面电源（已完结）\制作图纸和BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E302AAB1-7186-4D00-8C10-6DB1AD769CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEE4A7E-734A-4BAF-84EA-4A8601ADA72E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C6A72E4F-E85B-D44F-9281-2546847AAD39}"/>
   </bookViews>
@@ -3219,7 +3219,9 @@
       <c r="G54" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="H54" s="39"/>
+      <c r="H54" s="39">
+        <v>1</v>
+      </c>
       <c r="I54" s="51"/>
     </row>
     <row r="55" spans="1:9" ht="17.399999999999999">
